--- a/docs/downloads/04/tbl_other_educ_sex_alaotra_avaradrano.xlsx
+++ b/docs/downloads/04/tbl_other_educ_sex_alaotra_avaradrano.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E24"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -398,10 +398,10 @@
         </is>
       </c>
       <c r="D2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E2">
-        <v>20.5</v>
+        <v>19.9</v>
       </c>
     </row>
     <row r="3">
@@ -463,14 +463,14 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Secondaire 2ème cycle</t>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
         </is>
       </c>
       <c r="D5">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E5">
-        <v>9.6</v>
+        <v>10.9</v>
       </c>
     </row>
     <row r="6">
@@ -481,19 +481,19 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Femme</t>
+          <t>Homme</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Universitaire</t>
+          <t>Inconnu</t>
         </is>
       </c>
       <c r="D6">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="E6">
-        <v>0.6</v>
+        <v>32.6</v>
       </c>
     </row>
     <row r="7">
@@ -509,14 +509,14 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Inconnu</t>
+          <t>Primaire</t>
         </is>
       </c>
       <c r="D7">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="E7">
-        <v>37.1</v>
+        <v>50.6</v>
       </c>
     </row>
     <row r="8">
@@ -532,14 +532,14 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Primaire</t>
+          <t>Secondaire 1er cycle</t>
         </is>
       </c>
       <c r="D8">
-        <v>45</v>
+        <v>9</v>
       </c>
       <c r="E8">
-        <v>50.6</v>
+        <v>10.1</v>
       </c>
     </row>
     <row r="9">
@@ -555,14 +555,14 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Secondaire 1er cycle</t>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
         </is>
       </c>
       <c r="D9">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E9">
-        <v>10.1</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="10">
@@ -571,21 +571,10 @@
           <t>Alaotra - Avaradrano</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Homme</t>
-        </is>
-      </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Secondaire 2ème cycle</t>
-        </is>
-      </c>
-      <c r="D10">
-        <v>2</v>
-      </c>
-      <c r="E10">
-        <v>2.2</v>
+          <t>Inconnu</t>
+        </is>
       </c>
     </row>
     <row r="11">
@@ -596,32 +585,31 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Inconnu</t>
-        </is>
-      </c>
-      <c r="D11">
-        <v>1</v>
-      </c>
-      <c r="E11">
-        <v>33.3</v>
+          <t>Primaire</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Alaotra - Tous</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Femme</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Primaire</t>
+          <t>Inconnu</t>
         </is>
       </c>
       <c r="D12">
-        <v>2</v>
+        <v>180</v>
       </c>
       <c r="E12">
-        <v>66.7</v>
+        <v>20.5</v>
       </c>
     </row>
     <row r="13">
@@ -637,14 +625,14 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Inconnu</t>
+          <t>Primaire</t>
         </is>
       </c>
       <c r="D13">
-        <v>206</v>
+        <v>407</v>
       </c>
       <c r="E13">
-        <v>23.5</v>
+        <v>46.4</v>
       </c>
     </row>
     <row r="14">
@@ -660,14 +648,14 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Primaire</t>
+          <t>Secondaire 1er cycle</t>
         </is>
       </c>
       <c r="D14">
-        <v>407</v>
+        <v>195</v>
       </c>
       <c r="E14">
-        <v>46.4</v>
+        <v>22.2</v>
       </c>
     </row>
     <row r="15">
@@ -683,14 +671,14 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Secondaire 1er cycle</t>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
         </is>
       </c>
       <c r="D15">
-        <v>195</v>
+        <v>95</v>
       </c>
       <c r="E15">
-        <v>22.2</v>
+        <v>10.8</v>
       </c>
     </row>
     <row r="16">
@@ -701,19 +689,19 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Femme</t>
+          <t>Homme</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Secondaire 2ème cycle</t>
+          <t>Inconnu</t>
         </is>
       </c>
       <c r="D16">
-        <v>60</v>
+        <v>174</v>
       </c>
       <c r="E16">
-        <v>6.8</v>
+        <v>29.7</v>
       </c>
     </row>
     <row r="17">
@@ -724,19 +712,19 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Femme</t>
+          <t>Homme</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Universitaire</t>
+          <t>Primaire</t>
         </is>
       </c>
       <c r="D17">
-        <v>9</v>
+        <v>267</v>
       </c>
       <c r="E17">
-        <v>1</v>
+        <v>45.6</v>
       </c>
     </row>
     <row r="18">
@@ -752,14 +740,14 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Inconnu</t>
+          <t>Secondaire 1er cycle</t>
         </is>
       </c>
       <c r="D18">
-        <v>199</v>
+        <v>90</v>
       </c>
       <c r="E18">
-        <v>34</v>
+        <v>15.4</v>
       </c>
     </row>
     <row r="19">
@@ -775,14 +763,14 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Primaire</t>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
         </is>
       </c>
       <c r="D19">
-        <v>267</v>
+        <v>54</v>
       </c>
       <c r="E19">
-        <v>45.6</v>
+        <v>9.199999999999999</v>
       </c>
     </row>
     <row r="20">
@@ -791,21 +779,10 @@
           <t>Alaotra - Tous</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Homme</t>
-        </is>
-      </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Secondaire 1er cycle</t>
-        </is>
-      </c>
-      <c r="D20">
-        <v>90</v>
-      </c>
-      <c r="E20">
-        <v>15.4</v>
+          <t>Inconnu</t>
+        </is>
       </c>
     </row>
     <row r="21">
@@ -814,80 +791,10 @@
           <t>Alaotra - Tous</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Homme</t>
-        </is>
-      </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Secondaire 2ème cycle</t>
-        </is>
-      </c>
-      <c r="D21">
-        <v>26</v>
-      </c>
-      <c r="E21">
-        <v>4.4</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Alaotra - Tous</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Homme</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Universitaire</t>
-        </is>
-      </c>
-      <c r="D22">
-        <v>3</v>
-      </c>
-      <c r="E22">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Alaotra - Tous</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Inconnu</t>
-        </is>
-      </c>
-      <c r="D23">
-        <v>2</v>
-      </c>
-      <c r="E23">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Alaotra - Tous</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
           <t>Primaire</t>
         </is>
-      </c>
-      <c r="D24">
-        <v>3</v>
-      </c>
-      <c r="E24">
-        <v>60</v>
       </c>
     </row>
   </sheetData>

--- a/docs/downloads/04/tbl_other_educ_sex_alaotra_avaradrano.xlsx
+++ b/docs/downloads/04/tbl_other_educ_sex_alaotra_avaradrano.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E21"/>
+  <dimension ref="A1:E25"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -398,10 +398,10 @@
         </is>
       </c>
       <c r="D2">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="E2">
-        <v>19.9</v>
+        <v>5.1</v>
       </c>
     </row>
     <row r="3">
@@ -417,14 +417,14 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Primaire</t>
+          <t>Non scolarisé</t>
         </is>
       </c>
       <c r="D3">
-        <v>77</v>
+        <v>23</v>
       </c>
       <c r="E3">
-        <v>49.4</v>
+        <v>14.7</v>
       </c>
     </row>
     <row r="4">
@@ -440,14 +440,14 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Secondaire 1er cycle</t>
+          <t>Primaire</t>
         </is>
       </c>
       <c r="D4">
-        <v>31</v>
+        <v>77</v>
       </c>
       <c r="E4">
-        <v>19.9</v>
+        <v>49.4</v>
       </c>
     </row>
     <row r="5">
@@ -463,14 +463,14 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Secondaire 2ème cycle &amp; sup.</t>
+          <t>Secondaire 1er cycle</t>
         </is>
       </c>
       <c r="D5">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="E5">
-        <v>10.9</v>
+        <v>19.9</v>
       </c>
     </row>
     <row r="6">
@@ -481,19 +481,19 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Homme</t>
+          <t>Femme</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Inconnu</t>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
         </is>
       </c>
       <c r="D6">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="E6">
-        <v>32.6</v>
+        <v>10.9</v>
       </c>
     </row>
     <row r="7">
@@ -509,14 +509,14 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Primaire</t>
+          <t>Inconnu</t>
         </is>
       </c>
       <c r="D7">
-        <v>45</v>
+        <v>5</v>
       </c>
       <c r="E7">
-        <v>50.6</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="8">
@@ -532,14 +532,14 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Secondaire 1er cycle</t>
+          <t>Non scolarisé</t>
         </is>
       </c>
       <c r="D8">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="E8">
-        <v>10.1</v>
+        <v>27</v>
       </c>
     </row>
     <row r="9">
@@ -555,14 +555,14 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Secondaire 2ème cycle &amp; sup.</t>
+          <t>Primaire</t>
         </is>
       </c>
       <c r="D9">
-        <v>6</v>
+        <v>45</v>
       </c>
       <c r="E9">
-        <v>6.7</v>
+        <v>50.6</v>
       </c>
     </row>
     <row r="10">
@@ -571,10 +571,21 @@
           <t>Alaotra - Avaradrano</t>
         </is>
       </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Homme</t>
+        </is>
+      </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Inconnu</t>
-        </is>
+          <t>Secondaire 1er cycle</t>
+        </is>
+      </c>
+      <c r="D10">
+        <v>9</v>
+      </c>
+      <c r="E10">
+        <v>10.1</v>
       </c>
     </row>
     <row r="11">
@@ -583,56 +594,45 @@
           <t>Alaotra - Avaradrano</t>
         </is>
       </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Homme</t>
+        </is>
+      </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Primaire</t>
-        </is>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
+        </is>
+      </c>
+      <c r="D11">
+        <v>6</v>
+      </c>
+      <c r="E11">
+        <v>6.7</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Femme</t>
+          <t>Alaotra - Avaradrano</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Inconnu</t>
-        </is>
-      </c>
-      <c r="D12">
-        <v>180</v>
-      </c>
-      <c r="E12">
-        <v>20.5</v>
+          <t>Non scolarisé</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Femme</t>
+          <t>Alaotra - Avaradrano</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
           <t>Primaire</t>
         </is>
-      </c>
-      <c r="D13">
-        <v>407</v>
-      </c>
-      <c r="E13">
-        <v>46.4</v>
       </c>
     </row>
     <row r="14">
@@ -648,14 +648,14 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Secondaire 1er cycle</t>
+          <t>Inconnu</t>
         </is>
       </c>
       <c r="D14">
-        <v>195</v>
+        <v>47</v>
       </c>
       <c r="E14">
-        <v>22.2</v>
+        <v>5.4</v>
       </c>
     </row>
     <row r="15">
@@ -671,14 +671,14 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Secondaire 2ème cycle &amp; sup.</t>
+          <t>Non scolarisé</t>
         </is>
       </c>
       <c r="D15">
-        <v>95</v>
+        <v>133</v>
       </c>
       <c r="E15">
-        <v>10.8</v>
+        <v>15.2</v>
       </c>
     </row>
     <row r="16">
@@ -689,19 +689,19 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Homme</t>
+          <t>Femme</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Inconnu</t>
+          <t>Primaire</t>
         </is>
       </c>
       <c r="D16">
-        <v>174</v>
+        <v>407</v>
       </c>
       <c r="E16">
-        <v>29.7</v>
+        <v>46.4</v>
       </c>
     </row>
     <row r="17">
@@ -712,19 +712,19 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Homme</t>
+          <t>Femme</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Primaire</t>
+          <t>Secondaire 1er cycle</t>
         </is>
       </c>
       <c r="D17">
-        <v>267</v>
+        <v>195</v>
       </c>
       <c r="E17">
-        <v>45.6</v>
+        <v>22.2</v>
       </c>
     </row>
     <row r="18">
@@ -735,19 +735,19 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Homme</t>
+          <t>Femme</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Secondaire 1er cycle</t>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
         </is>
       </c>
       <c r="D18">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="E18">
-        <v>15.4</v>
+        <v>10.8</v>
       </c>
     </row>
     <row r="19">
@@ -763,14 +763,14 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Secondaire 2ème cycle &amp; sup.</t>
+          <t>Inconnu</t>
         </is>
       </c>
       <c r="D19">
-        <v>54</v>
+        <v>38</v>
       </c>
       <c r="E19">
-        <v>9.199999999999999</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="20">
@@ -779,10 +779,21 @@
           <t>Alaotra - Tous</t>
         </is>
       </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Homme</t>
+        </is>
+      </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Inconnu</t>
-        </is>
+          <t>Non scolarisé</t>
+        </is>
+      </c>
+      <c r="D20">
+        <v>136</v>
+      </c>
+      <c r="E20">
+        <v>23.2</v>
       </c>
     </row>
     <row r="21">
@@ -791,7 +802,88 @@
           <t>Alaotra - Tous</t>
         </is>
       </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Homme</t>
+        </is>
+      </c>
       <c r="C21" t="inlineStr">
+        <is>
+          <t>Primaire</t>
+        </is>
+      </c>
+      <c r="D21">
+        <v>267</v>
+      </c>
+      <c r="E21">
+        <v>45.6</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Alaotra - Tous</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Homme</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Secondaire 1er cycle</t>
+        </is>
+      </c>
+      <c r="D22">
+        <v>90</v>
+      </c>
+      <c r="E22">
+        <v>15.4</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Alaotra - Tous</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Homme</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
+        </is>
+      </c>
+      <c r="D23">
+        <v>54</v>
+      </c>
+      <c r="E23">
+        <v>9.199999999999999</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Alaotra - Tous</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Non scolarisé</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Alaotra - Tous</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
         <is>
           <t>Primaire</t>
         </is>
